--- a/vape_gr_data-Erin-20260525.xlsx
+++ b/vape_gr_data-Erin-20260525.xlsx
@@ -4078,7 +4078,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:M201"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
@@ -4134,7 +4134,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="2" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A2" s="8" t="s">
         <v>13</v>
       </c>
@@ -4175,7 +4175,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="3" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A3" s="8" t="s">
         <v>13</v>
       </c>
@@ -4216,7 +4216,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="4" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A4" s="8" t="s">
         <v>13</v>
       </c>
@@ -4257,7 +4257,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="5" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
@@ -4298,7 +4298,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="82.5" spans="1:13">
+    <row r="6" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
       <c r="A6" s="8" t="s">
         <v>13</v>
       </c>
@@ -4339,7 +4339,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="82.5" spans="1:13">
+    <row r="7" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
       <c r="A7" s="8" t="s">
         <v>13</v>
       </c>
@@ -4380,7 +4380,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="115.5" spans="1:13">
+    <row r="8" s="1" customFormat="1" ht="115.5" hidden="1" spans="1:13">
       <c r="A8" s="8" t="s">
         <v>13</v>
       </c>
@@ -4421,7 +4421,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="9" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A9" s="8" t="s">
         <v>13</v>
       </c>
@@ -4462,7 +4462,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="10" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A10" s="8" t="s">
         <v>13</v>
       </c>
@@ -4503,7 +4503,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="82.5" spans="1:13">
+    <row r="11" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
       <c r="A11" s="8" t="s">
         <v>13</v>
       </c>
@@ -4544,7 +4544,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="115.5" spans="1:13">
+    <row r="12" s="1" customFormat="1" ht="115.5" hidden="1" spans="1:13">
       <c r="A12" s="8" t="s">
         <v>13</v>
       </c>
@@ -4585,7 +4585,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="165" spans="1:13">
+    <row r="13" s="1" customFormat="1" ht="165" hidden="1" spans="1:13">
       <c r="A13" s="8" t="s">
         <v>13</v>
       </c>
@@ -4626,7 +4626,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="33" spans="1:13">
+    <row r="14" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
       <c r="A14" s="8" t="s">
         <v>13</v>
       </c>
@@ -4667,7 +4667,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="15" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A15" s="8" t="s">
         <v>13</v>
       </c>
@@ -4722,7 +4722,7 @@
         <v>90</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>91</v>
@@ -4749,7 +4749,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="17" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A17" s="8" t="s">
         <v>13</v>
       </c>
@@ -4831,7 +4831,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="33" spans="1:13">
+    <row r="19" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
       <c r="A19" s="8" t="s">
         <v>13</v>
       </c>
@@ -4872,7 +4872,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="49.5" spans="1:13">
+    <row r="20" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
       <c r="A20" s="8" t="s">
         <v>13</v>
       </c>
@@ -4913,7 +4913,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="82.5" spans="1:13">
+    <row r="21" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
       <c r="A21" s="8" t="s">
         <v>13</v>
       </c>
@@ -4954,7 +4954,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="22" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A22" s="8" t="s">
         <v>13</v>
       </c>
@@ -4995,7 +4995,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="49.5" spans="1:13">
+    <row r="23" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
       <c r="A23" s="8" t="s">
         <v>13</v>
       </c>
@@ -5036,7 +5036,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="24" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A24" s="8" t="s">
         <v>13</v>
       </c>
@@ -5077,7 +5077,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="82.5" spans="1:13">
+    <row r="25" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
       <c r="A25" s="8" t="s">
         <v>13</v>
       </c>
@@ -5118,7 +5118,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" ht="82.5" spans="1:13">
+    <row r="26" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
       <c r="A26" s="8" t="s">
         <v>13</v>
       </c>
@@ -5159,7 +5159,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" ht="49.5" spans="1:13">
+    <row r="27" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
       <c r="A27" s="8" t="s">
         <v>13</v>
       </c>
@@ -5200,7 +5200,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" ht="82.5" spans="1:13">
+    <row r="28" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
       <c r="A28" s="8" t="s">
         <v>13</v>
       </c>
@@ -5241,7 +5241,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" ht="49.5" spans="1:13">
+    <row r="29" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
       <c r="A29" s="8" t="s">
         <v>13</v>
       </c>
@@ -5282,7 +5282,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="30" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A30" s="8" t="s">
         <v>13</v>
       </c>
@@ -5323,7 +5323,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" ht="49.5" spans="1:13">
+    <row r="31" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
       <c r="A31" s="8" t="s">
         <v>13</v>
       </c>
@@ -5364,7 +5364,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="32" s="1" customFormat="1" ht="49.5" spans="1:13">
+    <row r="32" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
       <c r="A32" s="8" t="s">
         <v>13</v>
       </c>
@@ -5405,7 +5405,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="33" s="1" customFormat="1" ht="82.5" spans="1:13">
+    <row r="33" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
       <c r="A33" s="8" t="s">
         <v>13</v>
       </c>
@@ -5446,7 +5446,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" ht="82.5" spans="1:13">
+    <row r="34" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
       <c r="A34" s="8" t="s">
         <v>13</v>
       </c>
@@ -5487,7 +5487,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="35" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A35" s="8" t="s">
         <v>13</v>
       </c>
@@ -5528,7 +5528,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" ht="33" spans="1:13">
+    <row r="36" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
       <c r="A36" s="8" t="s">
         <v>13</v>
       </c>
@@ -5610,7 +5610,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" ht="99" spans="1:13">
+    <row r="38" s="1" customFormat="1" ht="99" hidden="1" spans="1:13">
       <c r="A38" s="8" t="s">
         <v>13</v>
       </c>
@@ -5651,7 +5651,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="39" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="39" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A39" s="8" t="s">
         <v>13</v>
       </c>
@@ -5692,7 +5692,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="40" s="1" customFormat="1" ht="49.5" spans="1:13">
+    <row r="40" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
       <c r="A40" s="8" t="s">
         <v>13</v>
       </c>
@@ -5733,7 +5733,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="41" s="1" customFormat="1" ht="49.5" spans="1:13">
+    <row r="41" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
       <c r="A41" s="8" t="s">
         <v>13</v>
       </c>
@@ -5774,7 +5774,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="42" s="1" customFormat="1" ht="247.5" spans="1:13">
+    <row r="42" s="1" customFormat="1" ht="247.5" hidden="1" spans="1:13">
       <c r="A42" s="8" t="s">
         <v>210</v>
       </c>
@@ -5815,7 +5815,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="43" s="1" customFormat="1" ht="99" spans="1:13">
+    <row r="43" s="1" customFormat="1" ht="99" hidden="1" spans="1:13">
       <c r="A43" s="8" t="s">
         <v>210</v>
       </c>
@@ -5856,7 +5856,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="44" s="1" customFormat="1" ht="82.5" spans="1:13">
+    <row r="44" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
       <c r="A44" s="8" t="s">
         <v>210</v>
       </c>
@@ -5897,7 +5897,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="45" s="1" customFormat="1" ht="99" spans="1:13">
+    <row r="45" s="1" customFormat="1" ht="99" hidden="1" spans="1:13">
       <c r="A45" s="8" t="s">
         <v>210</v>
       </c>
@@ -5938,7 +5938,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="46" s="1" customFormat="1" ht="82.5" spans="1:13">
+    <row r="46" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
       <c r="A46" s="8" t="s">
         <v>210</v>
       </c>
@@ -5979,7 +5979,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="47" s="1" customFormat="1" ht="82.5" spans="1:13">
+    <row r="47" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
       <c r="A47" s="8" t="s">
         <v>210</v>
       </c>
@@ -6020,7 +6020,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="48" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="48" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A48" s="8" t="s">
         <v>210</v>
       </c>
@@ -6061,7 +6061,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="49" s="1" customFormat="1" ht="99" spans="1:13">
+    <row r="49" s="1" customFormat="1" ht="99" hidden="1" spans="1:13">
       <c r="A49" s="8" t="s">
         <v>210</v>
       </c>
@@ -6102,7 +6102,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="50" s="1" customFormat="1" ht="82.5" spans="1:13">
+    <row r="50" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
       <c r="A50" s="8" t="s">
         <v>210</v>
       </c>
@@ -6143,7 +6143,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="51" s="1" customFormat="1" ht="198" spans="1:13">
+    <row r="51" s="1" customFormat="1" ht="198" hidden="1" spans="1:13">
       <c r="A51" s="8" t="s">
         <v>210</v>
       </c>
@@ -6184,7 +6184,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="52" s="1" customFormat="1" ht="198" spans="1:13">
+    <row r="52" s="1" customFormat="1" ht="198" hidden="1" spans="1:13">
       <c r="A52" s="8" t="s">
         <v>210</v>
       </c>
@@ -6225,7 +6225,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="53" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="53" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A53" s="8" t="s">
         <v>210</v>
       </c>
@@ -6266,7 +6266,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="54" s="1" customFormat="1" ht="82.5" spans="1:13">
+    <row r="54" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
       <c r="A54" s="8" t="s">
         <v>210</v>
       </c>
@@ -6307,7 +6307,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="55" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="55" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A55" s="8" t="s">
         <v>210</v>
       </c>
@@ -6348,7 +6348,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="56" s="1" customFormat="1" ht="231" spans="1:13">
+    <row r="56" s="1" customFormat="1" ht="231" hidden="1" spans="1:13">
       <c r="A56" s="8" t="s">
         <v>210</v>
       </c>
@@ -6389,7 +6389,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="57" s="1" customFormat="1" ht="198" spans="1:13">
+    <row r="57" s="1" customFormat="1" ht="198" hidden="1" spans="1:13">
       <c r="A57" s="8" t="s">
         <v>210</v>
       </c>
@@ -6430,7 +6430,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="58" s="1" customFormat="1" ht="165" spans="1:13">
+    <row r="58" s="1" customFormat="1" ht="165" hidden="1" spans="1:13">
       <c r="A58" s="8" t="s">
         <v>210</v>
       </c>
@@ -6471,7 +6471,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="59" s="1" customFormat="1" ht="33" spans="1:13">
+    <row r="59" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
       <c r="A59" s="8" t="s">
         <v>210</v>
       </c>
@@ -6512,7 +6512,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="60" s="1" customFormat="1" ht="165" spans="1:13">
+    <row r="60" s="1" customFormat="1" ht="165" hidden="1" spans="1:13">
       <c r="A60" s="8" t="s">
         <v>210</v>
       </c>
@@ -6553,7 +6553,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="61" s="1" customFormat="1" ht="181.5" spans="1:13">
+    <row r="61" s="1" customFormat="1" ht="181.5" hidden="1" spans="1:13">
       <c r="A61" s="8" t="s">
         <v>210</v>
       </c>
@@ -6594,7 +6594,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="62" s="1" customFormat="1" ht="99" spans="1:13">
+    <row r="62" s="1" customFormat="1" ht="99" hidden="1" spans="1:13">
       <c r="A62" s="8" t="s">
         <v>210</v>
       </c>
@@ -6635,7 +6635,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="63" s="1" customFormat="1" ht="99" spans="1:13">
+    <row r="63" s="1" customFormat="1" ht="99" hidden="1" spans="1:13">
       <c r="A63" s="8" t="s">
         <v>210</v>
       </c>
@@ -6676,7 +6676,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="64" s="1" customFormat="1" ht="181.5" spans="1:13">
+    <row r="64" s="1" customFormat="1" ht="181.5" hidden="1" spans="1:13">
       <c r="A64" s="8" t="s">
         <v>210</v>
       </c>
@@ -6717,7 +6717,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="65" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="65" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A65" s="8" t="s">
         <v>210</v>
       </c>
@@ -6758,7 +6758,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="66" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="66" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A66" s="8" t="s">
         <v>210</v>
       </c>
@@ -6799,7 +6799,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="67" s="1" customFormat="1" ht="115.5" spans="1:13">
+    <row r="67" s="1" customFormat="1" ht="115.5" hidden="1" spans="1:13">
       <c r="A67" s="8" t="s">
         <v>210</v>
       </c>
@@ -6840,7 +6840,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="68" s="1" customFormat="1" ht="82.5" spans="1:13">
+    <row r="68" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
       <c r="A68" s="8" t="s">
         <v>210</v>
       </c>
@@ -6881,7 +6881,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="69" s="1" customFormat="1" ht="132" spans="1:13">
+    <row r="69" s="1" customFormat="1" ht="132" hidden="1" spans="1:13">
       <c r="A69" s="8" t="s">
         <v>210</v>
       </c>
@@ -6922,7 +6922,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="70" s="1" customFormat="1" ht="214.5" spans="1:13">
+    <row r="70" s="1" customFormat="1" ht="214.5" hidden="1" spans="1:13">
       <c r="A70" s="8" t="s">
         <v>210</v>
       </c>
@@ -6963,7 +6963,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="71" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="71" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A71" s="8" t="s">
         <v>210</v>
       </c>
@@ -7004,7 +7004,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="72" s="1" customFormat="1" ht="49.5" spans="1:13">
+    <row r="72" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
       <c r="A72" s="8" t="s">
         <v>210</v>
       </c>
@@ -7045,7 +7045,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="73" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="73" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A73" s="8" t="s">
         <v>210</v>
       </c>
@@ -7086,7 +7086,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="74" s="1" customFormat="1" ht="99" spans="1:13">
+    <row r="74" s="1" customFormat="1" ht="99" hidden="1" spans="1:13">
       <c r="A74" s="8" t="s">
         <v>210</v>
       </c>
@@ -7127,7 +7127,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="75" s="1" customFormat="1" ht="33" spans="1:13">
+    <row r="75" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
       <c r="A75" s="8" t="s">
         <v>210</v>
       </c>
@@ -7168,7 +7168,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="76" s="1" customFormat="1" ht="181.5" spans="1:13">
+    <row r="76" s="1" customFormat="1" ht="181.5" hidden="1" spans="1:13">
       <c r="A76" s="8" t="s">
         <v>210</v>
       </c>
@@ -7209,7 +7209,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="77" s="1" customFormat="1" ht="82.5" spans="1:13">
+    <row r="77" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
       <c r="A77" s="8" t="s">
         <v>210</v>
       </c>
@@ -7250,7 +7250,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="78" s="1" customFormat="1" ht="99" spans="1:13">
+    <row r="78" s="1" customFormat="1" ht="99" hidden="1" spans="1:13">
       <c r="A78" s="8" t="s">
         <v>210</v>
       </c>
@@ -7291,7 +7291,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="79" s="1" customFormat="1" ht="82.5" spans="1:13">
+    <row r="79" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
       <c r="A79" s="8" t="s">
         <v>210</v>
       </c>
@@ -7332,7 +7332,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="80" s="1" customFormat="1" ht="148.5" spans="1:13">
+    <row r="80" s="1" customFormat="1" ht="148.5" hidden="1" spans="1:13">
       <c r="A80" s="8" t="s">
         <v>210</v>
       </c>
@@ -7373,7 +7373,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="81" s="1" customFormat="1" ht="49.5" spans="1:13">
+    <row r="81" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
       <c r="A81" s="8" t="s">
         <v>210</v>
       </c>
@@ -7414,7 +7414,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="82" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="82" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A82" s="8" t="s">
         <v>394</v>
       </c>
@@ -7455,7 +7455,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="83" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="83" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A83" s="8" t="s">
         <v>394</v>
       </c>
@@ -7496,7 +7496,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="84" s="1" customFormat="1" ht="49.5" spans="1:13">
+    <row r="84" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
       <c r="A84" s="8" t="s">
         <v>394</v>
       </c>
@@ -7537,7 +7537,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="85" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="85" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A85" s="8" t="s">
         <v>394</v>
       </c>
@@ -7578,7 +7578,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="86" s="1" customFormat="1" ht="33" spans="1:13">
+    <row r="86" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
       <c r="A86" s="8" t="s">
         <v>394</v>
       </c>
@@ -7619,7 +7619,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="87" s="1" customFormat="1" ht="132" spans="1:13">
+    <row r="87" s="1" customFormat="1" ht="132" hidden="1" spans="1:13">
       <c r="A87" s="8" t="s">
         <v>394</v>
       </c>
@@ -7660,7 +7660,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="88" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="88" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A88" s="8" t="s">
         <v>394</v>
       </c>
@@ -7701,7 +7701,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="89" s="1" customFormat="1" ht="82.5" spans="1:13">
+    <row r="89" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
       <c r="A89" s="8" t="s">
         <v>394</v>
       </c>
@@ -7742,7 +7742,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="90" s="1" customFormat="1" ht="33" spans="1:13">
+    <row r="90" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
       <c r="A90" s="8" t="s">
         <v>394</v>
       </c>
@@ -7783,7 +7783,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="91" s="1" customFormat="1" spans="1:13">
+    <row r="91" s="1" customFormat="1" hidden="1" spans="1:13">
       <c r="A91" s="8" t="s">
         <v>394</v>
       </c>
@@ -7824,7 +7824,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="92" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="92" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A92" s="8" t="s">
         <v>394</v>
       </c>
@@ -7865,7 +7865,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="93" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="93" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A93" s="8" t="s">
         <v>394</v>
       </c>
@@ -7906,7 +7906,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="94" s="1" customFormat="1" ht="115.5" spans="1:13">
+    <row r="94" s="1" customFormat="1" ht="115.5" hidden="1" spans="1:13">
       <c r="A94" s="8" t="s">
         <v>394</v>
       </c>
@@ -7947,7 +7947,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="95" s="1" customFormat="1" ht="33" spans="1:13">
+    <row r="95" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
       <c r="A95" s="8" t="s">
         <v>394</v>
       </c>
@@ -7988,7 +7988,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="96" s="1" customFormat="1" ht="49.5" spans="1:13">
+    <row r="96" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
       <c r="A96" s="8" t="s">
         <v>394</v>
       </c>
@@ -8029,7 +8029,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="97" s="1" customFormat="1" ht="33" spans="1:13">
+    <row r="97" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
       <c r="A97" s="8" t="s">
         <v>394</v>
       </c>
@@ -8070,7 +8070,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="98" s="1" customFormat="1" ht="49.5" spans="1:13">
+    <row r="98" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
       <c r="A98" s="8" t="s">
         <v>394</v>
       </c>
@@ -8111,7 +8111,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="99" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="99" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A99" s="8" t="s">
         <v>394</v>
       </c>
@@ -8152,7 +8152,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="100" s="1" customFormat="1" ht="49.5" spans="1:13">
+    <row r="100" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
       <c r="A100" s="8" t="s">
         <v>394</v>
       </c>
@@ -8193,7 +8193,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="101" s="1" customFormat="1" ht="82.5" spans="1:13">
+    <row r="101" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
       <c r="A101" s="8" t="s">
         <v>394</v>
       </c>
@@ -8234,7 +8234,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="102" s="1" customFormat="1" ht="33" spans="1:13">
+    <row r="102" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
       <c r="A102" s="8" t="s">
         <v>394</v>
       </c>
@@ -8275,7 +8275,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="103" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="103" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A103" s="8" t="s">
         <v>394</v>
       </c>
@@ -8316,7 +8316,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="104" s="1" customFormat="1" ht="49.5" spans="1:13">
+    <row r="104" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
       <c r="A104" s="8" t="s">
         <v>394</v>
       </c>
@@ -8357,7 +8357,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="105" s="1" customFormat="1" ht="82.5" spans="1:13">
+    <row r="105" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
       <c r="A105" s="8" t="s">
         <v>394</v>
       </c>
@@ -8398,7 +8398,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="106" s="1" customFormat="1" ht="49.5" spans="1:13">
+    <row r="106" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
       <c r="A106" s="8" t="s">
         <v>394</v>
       </c>
@@ -8439,7 +8439,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="107" s="1" customFormat="1" ht="82.5" spans="1:13">
+    <row r="107" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
       <c r="A107" s="8" t="s">
         <v>394</v>
       </c>
@@ -8480,7 +8480,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="108" s="1" customFormat="1" ht="33" spans="1:13">
+    <row r="108" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
       <c r="A108" s="8" t="s">
         <v>394</v>
       </c>
@@ -8521,7 +8521,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="109" s="1" customFormat="1" ht="49.5" spans="1:13">
+    <row r="109" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
       <c r="A109" s="8" t="s">
         <v>394</v>
       </c>
@@ -8562,7 +8562,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="110" s="1" customFormat="1" ht="49.5" spans="1:13">
+    <row r="110" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
       <c r="A110" s="8" t="s">
         <v>394</v>
       </c>
@@ -8603,7 +8603,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="111" s="1" customFormat="1" ht="132" spans="1:13">
+    <row r="111" s="1" customFormat="1" ht="132" hidden="1" spans="1:13">
       <c r="A111" s="8" t="s">
         <v>394</v>
       </c>
@@ -8644,7 +8644,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="112" s="1" customFormat="1" ht="99" spans="1:13">
+    <row r="112" s="1" customFormat="1" ht="99" hidden="1" spans="1:13">
       <c r="A112" s="8" t="s">
         <v>394</v>
       </c>
@@ -8685,7 +8685,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="113" s="1" customFormat="1" ht="99" spans="1:13">
+    <row r="113" s="1" customFormat="1" ht="99" hidden="1" spans="1:13">
       <c r="A113" s="8" t="s">
         <v>394</v>
       </c>
@@ -8726,7 +8726,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="114" s="1" customFormat="1" ht="82.5" spans="1:13">
+    <row r="114" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
       <c r="A114" s="8" t="s">
         <v>394</v>
       </c>
@@ -8767,7 +8767,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="115" s="1" customFormat="1" ht="132" spans="1:13">
+    <row r="115" s="1" customFormat="1" ht="132" hidden="1" spans="1:13">
       <c r="A115" s="8" t="s">
         <v>394</v>
       </c>
@@ -8808,7 +8808,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="116" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="116" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A116" s="8" t="s">
         <v>394</v>
       </c>
@@ -8849,7 +8849,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="117" s="1" customFormat="1" ht="49.5" spans="1:13">
+    <row r="117" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
       <c r="A117" s="8" t="s">
         <v>394</v>
       </c>
@@ -8890,7 +8890,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="118" s="1" customFormat="1" ht="198" spans="1:13">
+    <row r="118" s="1" customFormat="1" ht="198" hidden="1" spans="1:13">
       <c r="A118" s="8" t="s">
         <v>394</v>
       </c>
@@ -8931,7 +8931,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="119" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="119" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A119" s="8" t="s">
         <v>394</v>
       </c>
@@ -8972,7 +8972,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="120" s="1" customFormat="1" ht="115.5" spans="1:13">
+    <row r="120" s="1" customFormat="1" ht="115.5" hidden="1" spans="1:13">
       <c r="A120" s="8" t="s">
         <v>394</v>
       </c>
@@ -9013,7 +9013,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="121" s="1" customFormat="1" ht="99" spans="1:13">
+    <row r="121" s="1" customFormat="1" ht="99" hidden="1" spans="1:13">
       <c r="A121" s="8" t="s">
         <v>394</v>
       </c>
@@ -9054,7 +9054,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="122" s="1" customFormat="1" ht="33" spans="1:13">
+    <row r="122" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
       <c r="A122" s="2" t="s">
         <v>575</v>
       </c>
@@ -9095,7 +9095,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="123" s="1" customFormat="1" ht="82.5" spans="1:13">
+    <row r="123" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
       <c r="A123" s="2" t="s">
         <v>575</v>
       </c>
@@ -9136,7 +9136,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="124" s="1" customFormat="1" ht="33" spans="1:13">
+    <row r="124" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
       <c r="A124" s="2" t="s">
         <v>575</v>
       </c>
@@ -9177,7 +9177,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="125" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="125" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A125" s="2" t="s">
         <v>575</v>
       </c>
@@ -9218,7 +9218,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="126" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="126" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A126" s="2" t="s">
         <v>575</v>
       </c>
@@ -9259,7 +9259,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="127" s="1" customFormat="1" ht="33" spans="1:13">
+    <row r="127" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
       <c r="A127" s="2" t="s">
         <v>575</v>
       </c>
@@ -9300,7 +9300,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="128" s="1" customFormat="1" ht="82.5" spans="1:13">
+    <row r="128" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
       <c r="A128" s="2" t="s">
         <v>575</v>
       </c>
@@ -9341,7 +9341,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="129" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="129" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A129" s="2" t="s">
         <v>575</v>
       </c>
@@ -9382,7 +9382,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="130" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="130" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A130" s="2" t="s">
         <v>575</v>
       </c>
@@ -9423,7 +9423,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="131" s="1" customFormat="1" ht="82.5" spans="1:13">
+    <row r="131" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
       <c r="A131" s="2" t="s">
         <v>575</v>
       </c>
@@ -9464,7 +9464,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="132" s="1" customFormat="1" ht="33" spans="1:13">
+    <row r="132" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
       <c r="A132" s="2" t="s">
         <v>575</v>
       </c>
@@ -9505,7 +9505,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="133" s="1" customFormat="1" ht="33" spans="1:13">
+    <row r="133" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
       <c r="A133" s="2" t="s">
         <v>575</v>
       </c>
@@ -9546,7 +9546,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="134" s="1" customFormat="1" ht="33" spans="1:13">
+    <row r="134" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
       <c r="A134" s="2" t="s">
         <v>575</v>
       </c>
@@ -9587,7 +9587,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="135" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="135" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A135" s="2" t="s">
         <v>575</v>
       </c>
@@ -9628,7 +9628,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="136" s="1" customFormat="1" ht="82.5" spans="1:13">
+    <row r="136" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
       <c r="A136" s="2" t="s">
         <v>575</v>
       </c>
@@ -9669,7 +9669,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="137" s="1" customFormat="1" ht="33" spans="1:13">
+    <row r="137" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
       <c r="A137" s="2" t="s">
         <v>575</v>
       </c>
@@ -9710,7 +9710,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="138" s="1" customFormat="1" ht="82.5" spans="1:13">
+    <row r="138" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
       <c r="A138" s="2" t="s">
         <v>575</v>
       </c>
@@ -9751,7 +9751,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="139" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="139" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A139" s="2" t="s">
         <v>575</v>
       </c>
@@ -9792,7 +9792,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="140" s="1" customFormat="1" ht="33" spans="1:13">
+    <row r="140" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
       <c r="A140" s="2" t="s">
         <v>575</v>
       </c>
@@ -9833,7 +9833,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="141" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="141" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A141" s="2" t="s">
         <v>575</v>
       </c>
@@ -9874,7 +9874,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="142" s="1" customFormat="1" ht="115.5" spans="1:13">
+    <row r="142" s="1" customFormat="1" ht="115.5" hidden="1" spans="1:13">
       <c r="A142" s="2" t="s">
         <v>575</v>
       </c>
@@ -9915,7 +9915,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="143" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="143" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A143" s="2" t="s">
         <v>575</v>
       </c>
@@ -9956,7 +9956,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="144" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="144" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A144" s="2" t="s">
         <v>575</v>
       </c>
@@ -9997,7 +9997,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="145" s="1" customFormat="1" ht="49.5" spans="1:13">
+    <row r="145" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
       <c r="A145" s="2" t="s">
         <v>575</v>
       </c>
@@ -10038,7 +10038,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="146" s="1" customFormat="1" ht="49.5" spans="1:13">
+    <row r="146" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
       <c r="A146" s="2" t="s">
         <v>575</v>
       </c>
@@ -10079,7 +10079,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="147" s="1" customFormat="1" ht="181.5" spans="1:13">
+    <row r="147" s="1" customFormat="1" ht="181.5" hidden="1" spans="1:13">
       <c r="A147" s="2" t="s">
         <v>575</v>
       </c>
@@ -10120,7 +10120,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="148" s="1" customFormat="1" ht="49.5" spans="1:13">
+    <row r="148" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
       <c r="A148" s="2" t="s">
         <v>575</v>
       </c>
@@ -10161,7 +10161,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="149" s="1" customFormat="1" ht="49.5" spans="1:13">
+    <row r="149" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
       <c r="A149" s="2" t="s">
         <v>575</v>
       </c>
@@ -10202,7 +10202,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="150" s="1" customFormat="1" ht="49.5" spans="1:13">
+    <row r="150" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
       <c r="A150" s="2" t="s">
         <v>575</v>
       </c>
@@ -10243,7 +10243,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="151" s="1" customFormat="1" ht="49.5" spans="1:13">
+    <row r="151" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
       <c r="A151" s="2" t="s">
         <v>575</v>
       </c>
@@ -10284,7 +10284,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="152" s="1" customFormat="1" ht="165" spans="1:13">
+    <row r="152" s="1" customFormat="1" ht="165" hidden="1" spans="1:13">
       <c r="A152" s="2" t="s">
         <v>575</v>
       </c>
@@ -10325,7 +10325,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="153" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="153" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A153" s="2" t="s">
         <v>575</v>
       </c>
@@ -10366,7 +10366,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="154" s="1" customFormat="1" ht="82.5" spans="1:13">
+    <row r="154" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
       <c r="A154" s="2" t="s">
         <v>575</v>
       </c>
@@ -10407,7 +10407,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="155" s="1" customFormat="1" ht="49.5" spans="1:13">
+    <row r="155" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
       <c r="A155" s="2" t="s">
         <v>575</v>
       </c>
@@ -10448,7 +10448,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="156" s="1" customFormat="1" ht="49.5" spans="1:13">
+    <row r="156" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
       <c r="A156" s="2" t="s">
         <v>575</v>
       </c>
@@ -10489,7 +10489,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="157" s="1" customFormat="1" ht="33" spans="1:13">
+    <row r="157" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
       <c r="A157" s="2" t="s">
         <v>575</v>
       </c>
@@ -10530,7 +10530,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="158" s="1" customFormat="1" ht="66" spans="1:13">
+    <row r="158" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
       <c r="A158" s="2" t="s">
         <v>575</v>
       </c>
@@ -10571,7 +10571,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="159" s="1" customFormat="1" ht="132" spans="1:13">
+    <row r="159" s="1" customFormat="1" ht="132" hidden="1" spans="1:13">
       <c r="A159" s="2" t="s">
         <v>575</v>
       </c>
@@ -10612,7 +10612,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="160" s="1" customFormat="1" ht="82.5" spans="1:13">
+    <row r="160" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
       <c r="A160" s="2" t="s">
         <v>575</v>
       </c>
@@ -10653,7 +10653,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="161" ht="66" spans="1:13">
+    <row r="161" ht="66" hidden="1" spans="1:13">
       <c r="A161" s="2" t="s">
         <v>575</v>
       </c>
@@ -10694,7 +10694,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="162" ht="330" spans="1:13">
+    <row r="162" ht="330" hidden="1" spans="1:13">
       <c r="A162" s="2" t="s">
         <v>750</v>
       </c>
@@ -10735,7 +10735,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="163" spans="1:13">
+    <row r="163" hidden="1" spans="1:13">
       <c r="A163" s="2" t="s">
         <v>750</v>
       </c>
@@ -10776,7 +10776,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="164" spans="1:13">
+    <row r="164" hidden="1" spans="1:13">
       <c r="A164" s="2" t="s">
         <v>750</v>
       </c>
@@ -10817,7 +10817,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="165" spans="1:13">
+    <row r="165" hidden="1" spans="1:13">
       <c r="A165" s="2" t="s">
         <v>750</v>
       </c>
@@ -10858,7 +10858,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="166" spans="1:13">
+    <row r="166" hidden="1" spans="1:13">
       <c r="A166" s="2" t="s">
         <v>750</v>
       </c>
@@ -10899,7 +10899,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="167" spans="1:13">
+    <row r="167" hidden="1" spans="1:13">
       <c r="A167" s="2" t="s">
         <v>750</v>
       </c>
@@ -10940,7 +10940,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="168" spans="1:13">
+    <row r="168" hidden="1" spans="1:13">
       <c r="A168" s="2" t="s">
         <v>750</v>
       </c>
@@ -10981,7 +10981,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="169" ht="33" spans="1:13">
+    <row r="169" ht="33" hidden="1" spans="1:13">
       <c r="A169" s="2" t="s">
         <v>750</v>
       </c>
@@ -11022,7 +11022,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="170" spans="1:13">
+    <row r="170" hidden="1" spans="1:13">
       <c r="A170" s="2" t="s">
         <v>750</v>
       </c>
@@ -11063,7 +11063,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="171" spans="1:13">
+    <row r="171" hidden="1" spans="1:13">
       <c r="A171" s="2" t="s">
         <v>750</v>
       </c>
@@ -11104,7 +11104,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="172" spans="1:13">
+    <row r="172" hidden="1" spans="1:13">
       <c r="A172" s="2" t="s">
         <v>750</v>
       </c>
@@ -11145,7 +11145,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="173" spans="1:13">
+    <row r="173" hidden="1" spans="1:13">
       <c r="A173" s="2" t="s">
         <v>750</v>
       </c>
@@ -11186,7 +11186,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="174" spans="1:13">
+    <row r="174" hidden="1" spans="1:13">
       <c r="A174" s="2" t="s">
         <v>750</v>
       </c>
@@ -11227,7 +11227,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="175" spans="1:13">
+    <row r="175" hidden="1" spans="1:13">
       <c r="A175" s="2" t="s">
         <v>750</v>
       </c>
@@ -11268,7 +11268,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="176" spans="1:13">
+    <row r="176" hidden="1" spans="1:13">
       <c r="A176" s="2" t="s">
         <v>750</v>
       </c>
@@ -11309,7 +11309,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="177" spans="1:13">
+    <row r="177" hidden="1" spans="1:13">
       <c r="A177" s="2" t="s">
         <v>750</v>
       </c>
@@ -11350,7 +11350,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="178" spans="1:13">
+    <row r="178" hidden="1" spans="1:13">
       <c r="A178" s="2" t="s">
         <v>750</v>
       </c>
@@ -11391,7 +11391,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="179" spans="1:13">
+    <row r="179" hidden="1" spans="1:13">
       <c r="A179" s="2" t="s">
         <v>750</v>
       </c>
@@ -11432,7 +11432,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="180" spans="1:13">
+    <row r="180" hidden="1" spans="1:13">
       <c r="A180" s="2" t="s">
         <v>750</v>
       </c>
@@ -11473,7 +11473,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="181" spans="1:13">
+    <row r="181" hidden="1" spans="1:13">
       <c r="A181" s="2" t="s">
         <v>750</v>
       </c>
@@ -11514,7 +11514,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="182" ht="33" spans="1:13">
+    <row r="182" ht="33" hidden="1" spans="1:13">
       <c r="A182" s="2" t="s">
         <v>750</v>
       </c>
@@ -11555,7 +11555,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="183" ht="49.5" spans="1:13">
+    <row r="183" ht="49.5" hidden="1" spans="1:13">
       <c r="A183" s="2" t="s">
         <v>750</v>
       </c>
@@ -11596,7 +11596,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="184" ht="49.5" spans="1:13">
+    <row r="184" ht="49.5" hidden="1" spans="1:13">
       <c r="A184" s="2" t="s">
         <v>750</v>
       </c>
@@ -11637,7 +11637,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="185" ht="49.5" spans="1:13">
+    <row r="185" ht="49.5" hidden="1" spans="1:13">
       <c r="A185" s="2" t="s">
         <v>750</v>
       </c>
@@ -11678,7 +11678,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="186" ht="49.5" spans="1:13">
+    <row r="186" ht="49.5" hidden="1" spans="1:13">
       <c r="A186" s="2" t="s">
         <v>750</v>
       </c>
@@ -11719,7 +11719,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="187" ht="66" spans="1:13">
+    <row r="187" ht="66" hidden="1" spans="1:13">
       <c r="A187" s="2" t="s">
         <v>750</v>
       </c>
@@ -11760,7 +11760,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="188" ht="82.5" spans="1:13">
+    <row r="188" ht="82.5" hidden="1" spans="1:13">
       <c r="A188" s="2" t="s">
         <v>750</v>
       </c>
@@ -11801,7 +11801,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="189" ht="66" spans="1:13">
+    <row r="189" ht="66" hidden="1" spans="1:13">
       <c r="A189" s="2" t="s">
         <v>750</v>
       </c>
@@ -11842,7 +11842,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="190" ht="33" spans="1:13">
+    <row r="190" ht="33" hidden="1" spans="1:13">
       <c r="A190" s="2" t="s">
         <v>750</v>
       </c>
@@ -11883,7 +11883,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="191" ht="33" spans="1:13">
+    <row r="191" ht="33" hidden="1" spans="1:13">
       <c r="A191" s="2" t="s">
         <v>750</v>
       </c>
@@ -11924,7 +11924,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="192" ht="33" spans="1:13">
+    <row r="192" ht="33" hidden="1" spans="1:13">
       <c r="A192" s="2" t="s">
         <v>750</v>
       </c>
@@ -11965,7 +11965,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="193" ht="49.5" spans="1:13">
+    <row r="193" ht="49.5" hidden="1" spans="1:13">
       <c r="A193" s="2" t="s">
         <v>750</v>
       </c>
@@ -12006,7 +12006,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="194" ht="82.5" spans="1:13">
+    <row r="194" ht="82.5" hidden="1" spans="1:13">
       <c r="A194" s="2" t="s">
         <v>750</v>
       </c>
@@ -12047,7 +12047,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="195" ht="66" spans="1:13">
+    <row r="195" ht="66" hidden="1" spans="1:13">
       <c r="A195" s="2" t="s">
         <v>750</v>
       </c>
@@ -12088,7 +12088,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="196" ht="33" spans="1:13">
+    <row r="196" ht="33" hidden="1" spans="1:13">
       <c r="A196" s="2" t="s">
         <v>750</v>
       </c>
@@ -12129,7 +12129,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="197" ht="33" spans="1:13">
+    <row r="197" ht="33" hidden="1" spans="1:13">
       <c r="A197" s="2" t="s">
         <v>750</v>
       </c>
@@ -12170,7 +12170,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="198" ht="33" spans="1:13">
+    <row r="198" ht="33" hidden="1" spans="1:13">
       <c r="A198" s="2" t="s">
         <v>750</v>
       </c>
@@ -12211,7 +12211,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="199" ht="33" spans="1:13">
+    <row r="199" ht="33" hidden="1" spans="1:13">
       <c r="A199" s="2" t="s">
         <v>750</v>
       </c>
@@ -12252,7 +12252,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="200" ht="33" spans="1:13">
+    <row r="200" ht="33" hidden="1" spans="1:13">
       <c r="A200" s="2" t="s">
         <v>750</v>
       </c>
@@ -12293,7 +12293,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="201" ht="49.5" spans="1:13">
+    <row r="201" ht="49.5" hidden="1" spans="1:13">
       <c r="A201" s="2" t="s">
         <v>750</v>
       </c>
@@ -12336,6 +12336,11 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:M201" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="TNT Vape"/>
+      </filters>
+    </filterColumn>
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/vape_gr_data-Erin-20260525.xlsx
+++ b/vape_gr_data-Erin-20260525.xlsx
@@ -1590,22 +1590,22 @@
     <t>https://vapexperts.gr/ygra-anaplirosis/flavour-shots/flavour-shots-60ml/lacrema-60ml-vnv-liquids-detail</t>
   </si>
   <si>
+    <t>Butter Cookie</t>
+  </si>
+  <si>
+    <t>Το βραβευμένο υγρό Timekeeper! Το καλύτερο Μπισκότο Βουτύρου Ζάχαρης που θα έχετε δοκιμάσει ποτέ!</t>
+  </si>
+  <si>
+    <t>The award-winning Timekeeper liquid! The best Sugar Butter Cookie you'll ever taste!</t>
+  </si>
+  <si>
+    <t>https://vapexperts.gr/ygra-anaplirosis/flavour-shots/flavour-shots-120ml/timekeeper-120ml-by-steam-train-detail</t>
+  </si>
+  <si>
     <t>Η γλυκιά και έντονα εθιστική φρουτώδης γεύση των παγωμένων σταφυλιών σε συνδυασμό με πράσινα, τραγανά μήλα δίνει σε αυτό το υγρό μια εξωπραγματική υπόσταση που θα σας συναρπάσει!</t>
   </si>
   <si>
-    <t>The sweet and intensely addictive fruity flavor of frozen grapes, combined with crisp green apples, gives this drink an otherworldly quality that will captivate you!</t>
-  </si>
-  <si>
-    <t>https://vapexperts.gr/ygra-anaplirosis/flavour-shots/flavour-shots-120ml/timekeeper-120ml-by-steam-train-detail</t>
-  </si>
-  <si>
-    <t>Butter Cookie</t>
-  </si>
-  <si>
-    <t>Το βραβευμένο υγρό Timekeeper! Το καλύτερο Μπισκότο Βουτύρου Ζάχαρης που θα έχετε δοκιμάσει ποτέ!</t>
-  </si>
-  <si>
-    <t>The award-winning Timekeeper syrup! The best butter-sugar cookie you’ve ever tasted!</t>
+    <t>The sweet and intensely addictive fruity flavor of frozen grapes combined with green, crisp apples gives this liquid an unreal essence that will fascinate you!</t>
   </si>
   <si>
     <t>https://vapexperts.gr/ygra-anaplirosis/flavour-shots/flavour-shots-120ml/all-aboard-120ml-by-steam-train-detail</t>
@@ -4078,7 +4078,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
+  <sheetPr/>
   <dimension ref="A1:M201"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
@@ -4134,7 +4134,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="2" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A2" s="8" t="s">
         <v>13</v>
       </c>
@@ -4175,7 +4175,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="3" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A3" s="8" t="s">
         <v>13</v>
       </c>
@@ -4216,7 +4216,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="4" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A4" s="8" t="s">
         <v>13</v>
       </c>
@@ -4257,7 +4257,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="5" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
@@ -4298,7 +4298,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
+    <row r="6" s="1" customFormat="1" ht="82.5" spans="1:13">
       <c r="A6" s="8" t="s">
         <v>13</v>
       </c>
@@ -4330,7 +4330,7 @@
         <v>35</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="L6" s="8" t="s">
         <v>36</v>
@@ -4339,7 +4339,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
+    <row r="7" s="1" customFormat="1" ht="82.5" spans="1:13">
       <c r="A7" s="8" t="s">
         <v>13</v>
       </c>
@@ -4380,7 +4380,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="115.5" hidden="1" spans="1:13">
+    <row r="8" s="1" customFormat="1" ht="115.5" spans="1:13">
       <c r="A8" s="8" t="s">
         <v>13</v>
       </c>
@@ -4421,7 +4421,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="9" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A9" s="8" t="s">
         <v>13</v>
       </c>
@@ -4462,7 +4462,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="10" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A10" s="8" t="s">
         <v>13</v>
       </c>
@@ -4503,7 +4503,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
+    <row r="11" s="1" customFormat="1" ht="82.5" spans="1:13">
       <c r="A11" s="8" t="s">
         <v>13</v>
       </c>
@@ -4544,7 +4544,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="115.5" hidden="1" spans="1:13">
+    <row r="12" s="1" customFormat="1" ht="115.5" spans="1:13">
       <c r="A12" s="8" t="s">
         <v>13</v>
       </c>
@@ -4585,7 +4585,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="165" hidden="1" spans="1:13">
+    <row r="13" s="1" customFormat="1" ht="165" spans="1:13">
       <c r="A13" s="8" t="s">
         <v>13</v>
       </c>
@@ -4626,7 +4626,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
+    <row r="14" s="1" customFormat="1" ht="33" spans="1:13">
       <c r="A14" s="8" t="s">
         <v>13</v>
       </c>
@@ -4667,7 +4667,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="15" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A15" s="8" t="s">
         <v>13</v>
       </c>
@@ -4749,7 +4749,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="17" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A17" s="8" t="s">
         <v>13</v>
       </c>
@@ -4831,7 +4831,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
+    <row r="19" s="1" customFormat="1" ht="33" spans="1:13">
       <c r="A19" s="8" t="s">
         <v>13</v>
       </c>
@@ -4860,7 +4860,7 @@
         <v>108</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="K19" s="8" t="s">
         <v>16</v>
@@ -4872,7 +4872,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
+    <row r="20" s="1" customFormat="1" ht="49.5" spans="1:13">
       <c r="A20" s="8" t="s">
         <v>13</v>
       </c>
@@ -4913,7 +4913,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
+    <row r="21" s="1" customFormat="1" ht="82.5" spans="1:13">
       <c r="A21" s="8" t="s">
         <v>13</v>
       </c>
@@ -4954,7 +4954,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="22" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A22" s="8" t="s">
         <v>13</v>
       </c>
@@ -4986,7 +4986,7 @@
         <v>35</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="L22" s="8" t="s">
         <v>36</v>
@@ -4995,7 +4995,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
+    <row r="23" s="1" customFormat="1" ht="49.5" spans="1:13">
       <c r="A23" s="8" t="s">
         <v>13</v>
       </c>
@@ -5036,7 +5036,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="24" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A24" s="8" t="s">
         <v>13</v>
       </c>
@@ -5077,7 +5077,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
+    <row r="25" s="1" customFormat="1" ht="82.5" spans="1:13">
       <c r="A25" s="8" t="s">
         <v>13</v>
       </c>
@@ -5118,7 +5118,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
+    <row r="26" s="1" customFormat="1" ht="82.5" spans="1:13">
       <c r="A26" s="8" t="s">
         <v>13</v>
       </c>
@@ -5159,7 +5159,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
+    <row r="27" s="1" customFormat="1" ht="49.5" spans="1:13">
       <c r="A27" s="8" t="s">
         <v>13</v>
       </c>
@@ -5200,7 +5200,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
+    <row r="28" s="1" customFormat="1" ht="82.5" spans="1:13">
       <c r="A28" s="8" t="s">
         <v>13</v>
       </c>
@@ -5241,7 +5241,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
+    <row r="29" s="1" customFormat="1" ht="49.5" spans="1:13">
       <c r="A29" s="8" t="s">
         <v>13</v>
       </c>
@@ -5282,7 +5282,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="30" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A30" s="8" t="s">
         <v>13</v>
       </c>
@@ -5323,7 +5323,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
+    <row r="31" s="1" customFormat="1" ht="49.5" spans="1:13">
       <c r="A31" s="8" t="s">
         <v>13</v>
       </c>
@@ -5364,7 +5364,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="32" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
+    <row r="32" s="1" customFormat="1" ht="49.5" spans="1:13">
       <c r="A32" s="8" t="s">
         <v>13</v>
       </c>
@@ -5405,7 +5405,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="33" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
+    <row r="33" s="1" customFormat="1" ht="82.5" spans="1:13">
       <c r="A33" s="8" t="s">
         <v>13</v>
       </c>
@@ -5446,7 +5446,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
+    <row r="34" s="1" customFormat="1" ht="82.5" spans="1:13">
       <c r="A34" s="8" t="s">
         <v>13</v>
       </c>
@@ -5487,7 +5487,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="35" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A35" s="8" t="s">
         <v>13</v>
       </c>
@@ -5528,7 +5528,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
+    <row r="36" s="1" customFormat="1" ht="33" spans="1:13">
       <c r="A36" s="8" t="s">
         <v>13</v>
       </c>
@@ -5610,7 +5610,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" ht="99" hidden="1" spans="1:13">
+    <row r="38" s="1" customFormat="1" ht="99" spans="1:13">
       <c r="A38" s="8" t="s">
         <v>13</v>
       </c>
@@ -5639,7 +5639,7 @@
         <v>197</v>
       </c>
       <c r="J38" s="8" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="K38" s="8" t="s">
         <v>16</v>
@@ -5651,7 +5651,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="39" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="39" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A39" s="8" t="s">
         <v>13</v>
       </c>
@@ -5692,7 +5692,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="40" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
+    <row r="40" s="1" customFormat="1" ht="49.5" spans="1:13">
       <c r="A40" s="8" t="s">
         <v>13</v>
       </c>
@@ -5733,7 +5733,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="41" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
+    <row r="41" s="1" customFormat="1" ht="49.5" spans="1:13">
       <c r="A41" s="8" t="s">
         <v>13</v>
       </c>
@@ -5774,7 +5774,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="42" s="1" customFormat="1" ht="247.5" hidden="1" spans="1:13">
+    <row r="42" s="1" customFormat="1" ht="247.5" spans="1:13">
       <c r="A42" s="8" t="s">
         <v>210</v>
       </c>
@@ -5815,7 +5815,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="43" s="1" customFormat="1" ht="99" hidden="1" spans="1:13">
+    <row r="43" s="1" customFormat="1" ht="99" spans="1:13">
       <c r="A43" s="8" t="s">
         <v>210</v>
       </c>
@@ -5856,7 +5856,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="44" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
+    <row r="44" s="1" customFormat="1" ht="82.5" spans="1:13">
       <c r="A44" s="8" t="s">
         <v>210</v>
       </c>
@@ -5897,7 +5897,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="45" s="1" customFormat="1" ht="99" hidden="1" spans="1:13">
+    <row r="45" s="1" customFormat="1" ht="99" spans="1:13">
       <c r="A45" s="8" t="s">
         <v>210</v>
       </c>
@@ -5938,7 +5938,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="46" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
+    <row r="46" s="1" customFormat="1" ht="82.5" spans="1:13">
       <c r="A46" s="8" t="s">
         <v>210</v>
       </c>
@@ -5979,7 +5979,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="47" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
+    <row r="47" s="1" customFormat="1" ht="82.5" spans="1:13">
       <c r="A47" s="8" t="s">
         <v>210</v>
       </c>
@@ -6020,7 +6020,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="48" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="48" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A48" s="8" t="s">
         <v>210</v>
       </c>
@@ -6061,7 +6061,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="49" s="1" customFormat="1" ht="99" hidden="1" spans="1:13">
+    <row r="49" s="1" customFormat="1" ht="99" spans="1:13">
       <c r="A49" s="8" t="s">
         <v>210</v>
       </c>
@@ -6102,7 +6102,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="50" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
+    <row r="50" s="1" customFormat="1" ht="82.5" spans="1:13">
       <c r="A50" s="8" t="s">
         <v>210</v>
       </c>
@@ -6143,7 +6143,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="51" s="1" customFormat="1" ht="198" hidden="1" spans="1:13">
+    <row r="51" s="1" customFormat="1" ht="198" spans="1:13">
       <c r="A51" s="8" t="s">
         <v>210</v>
       </c>
@@ -6184,7 +6184,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="52" s="1" customFormat="1" ht="198" hidden="1" spans="1:13">
+    <row r="52" s="1" customFormat="1" ht="198" spans="1:13">
       <c r="A52" s="8" t="s">
         <v>210</v>
       </c>
@@ -6225,7 +6225,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="53" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="53" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A53" s="8" t="s">
         <v>210</v>
       </c>
@@ -6266,7 +6266,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="54" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
+    <row r="54" s="1" customFormat="1" ht="82.5" spans="1:13">
       <c r="A54" s="8" t="s">
         <v>210</v>
       </c>
@@ -6307,7 +6307,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="55" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="55" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A55" s="8" t="s">
         <v>210</v>
       </c>
@@ -6348,7 +6348,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="56" s="1" customFormat="1" ht="231" hidden="1" spans="1:13">
+    <row r="56" s="1" customFormat="1" ht="231" spans="1:13">
       <c r="A56" s="8" t="s">
         <v>210</v>
       </c>
@@ -6389,7 +6389,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="57" s="1" customFormat="1" ht="198" hidden="1" spans="1:13">
+    <row r="57" s="1" customFormat="1" ht="198" spans="1:13">
       <c r="A57" s="8" t="s">
         <v>210</v>
       </c>
@@ -6430,7 +6430,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="58" s="1" customFormat="1" ht="165" hidden="1" spans="1:13">
+    <row r="58" s="1" customFormat="1" ht="165" spans="1:13">
       <c r="A58" s="8" t="s">
         <v>210</v>
       </c>
@@ -6471,7 +6471,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="59" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
+    <row r="59" s="1" customFormat="1" ht="33" spans="1:13">
       <c r="A59" s="8" t="s">
         <v>210</v>
       </c>
@@ -6512,7 +6512,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="60" s="1" customFormat="1" ht="165" hidden="1" spans="1:13">
+    <row r="60" s="1" customFormat="1" ht="165" spans="1:13">
       <c r="A60" s="8" t="s">
         <v>210</v>
       </c>
@@ -6553,7 +6553,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="61" s="1" customFormat="1" ht="181.5" hidden="1" spans="1:13">
+    <row r="61" s="1" customFormat="1" ht="181.5" spans="1:13">
       <c r="A61" s="8" t="s">
         <v>210</v>
       </c>
@@ -6594,7 +6594,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="62" s="1" customFormat="1" ht="99" hidden="1" spans="1:13">
+    <row r="62" s="1" customFormat="1" ht="99" spans="1:13">
       <c r="A62" s="8" t="s">
         <v>210</v>
       </c>
@@ -6635,7 +6635,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="63" s="1" customFormat="1" ht="99" hidden="1" spans="1:13">
+    <row r="63" s="1" customFormat="1" ht="99" spans="1:13">
       <c r="A63" s="8" t="s">
         <v>210</v>
       </c>
@@ -6676,7 +6676,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="64" s="1" customFormat="1" ht="181.5" hidden="1" spans="1:13">
+    <row r="64" s="1" customFormat="1" ht="181.5" spans="1:13">
       <c r="A64" s="8" t="s">
         <v>210</v>
       </c>
@@ -6717,7 +6717,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="65" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="65" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A65" s="8" t="s">
         <v>210</v>
       </c>
@@ -6758,7 +6758,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="66" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="66" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A66" s="8" t="s">
         <v>210</v>
       </c>
@@ -6799,7 +6799,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="67" s="1" customFormat="1" ht="115.5" hidden="1" spans="1:13">
+    <row r="67" s="1" customFormat="1" ht="115.5" spans="1:13">
       <c r="A67" s="8" t="s">
         <v>210</v>
       </c>
@@ -6840,7 +6840,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="68" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
+    <row r="68" s="1" customFormat="1" ht="82.5" spans="1:13">
       <c r="A68" s="8" t="s">
         <v>210</v>
       </c>
@@ -6872,7 +6872,7 @@
         <v>16</v>
       </c>
       <c r="K68" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="L68" s="8" t="s">
         <v>36</v>
@@ -6881,7 +6881,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="69" s="1" customFormat="1" ht="132" hidden="1" spans="1:13">
+    <row r="69" s="1" customFormat="1" ht="132" spans="1:13">
       <c r="A69" s="8" t="s">
         <v>210</v>
       </c>
@@ -6922,7 +6922,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="70" s="1" customFormat="1" ht="214.5" hidden="1" spans="1:13">
+    <row r="70" s="1" customFormat="1" ht="214.5" spans="1:13">
       <c r="A70" s="8" t="s">
         <v>210</v>
       </c>
@@ -6963,7 +6963,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="71" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="71" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A71" s="8" t="s">
         <v>210</v>
       </c>
@@ -7004,7 +7004,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="72" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
+    <row r="72" s="1" customFormat="1" ht="49.5" spans="1:13">
       <c r="A72" s="8" t="s">
         <v>210</v>
       </c>
@@ -7045,7 +7045,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="73" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="73" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A73" s="8" t="s">
         <v>210</v>
       </c>
@@ -7086,7 +7086,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="74" s="1" customFormat="1" ht="99" hidden="1" spans="1:13">
+    <row r="74" s="1" customFormat="1" ht="99" spans="1:13">
       <c r="A74" s="8" t="s">
         <v>210</v>
       </c>
@@ -7127,7 +7127,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="75" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
+    <row r="75" s="1" customFormat="1" ht="33" spans="1:13">
       <c r="A75" s="8" t="s">
         <v>210</v>
       </c>
@@ -7168,7 +7168,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="76" s="1" customFormat="1" ht="181.5" hidden="1" spans="1:13">
+    <row r="76" s="1" customFormat="1" ht="181.5" spans="1:13">
       <c r="A76" s="8" t="s">
         <v>210</v>
       </c>
@@ -7209,7 +7209,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="77" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
+    <row r="77" s="1" customFormat="1" ht="82.5" spans="1:13">
       <c r="A77" s="8" t="s">
         <v>210</v>
       </c>
@@ -7250,7 +7250,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="78" s="1" customFormat="1" ht="99" hidden="1" spans="1:13">
+    <row r="78" s="1" customFormat="1" ht="99" spans="1:13">
       <c r="A78" s="8" t="s">
         <v>210</v>
       </c>
@@ -7291,7 +7291,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="79" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
+    <row r="79" s="1" customFormat="1" ht="82.5" spans="1:13">
       <c r="A79" s="8" t="s">
         <v>210</v>
       </c>
@@ -7332,7 +7332,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="80" s="1" customFormat="1" ht="148.5" hidden="1" spans="1:13">
+    <row r="80" s="1" customFormat="1" ht="148.5" spans="1:13">
       <c r="A80" s="8" t="s">
         <v>210</v>
       </c>
@@ -7361,7 +7361,7 @@
         <v>388</v>
       </c>
       <c r="J80" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K80" s="8" t="s">
         <v>16</v>
@@ -7373,7 +7373,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="81" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
+    <row r="81" s="1" customFormat="1" ht="49.5" spans="1:13">
       <c r="A81" s="8" t="s">
         <v>210</v>
       </c>
@@ -7414,7 +7414,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="82" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="82" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A82" s="8" t="s">
         <v>394</v>
       </c>
@@ -7455,7 +7455,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="83" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="83" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A83" s="8" t="s">
         <v>394</v>
       </c>
@@ -7496,7 +7496,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="84" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
+    <row r="84" s="1" customFormat="1" ht="49.5" spans="1:13">
       <c r="A84" s="8" t="s">
         <v>394</v>
       </c>
@@ -7537,7 +7537,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="85" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="85" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A85" s="8" t="s">
         <v>394</v>
       </c>
@@ -7578,7 +7578,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="86" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
+    <row r="86" s="1" customFormat="1" ht="33" spans="1:13">
       <c r="A86" s="8" t="s">
         <v>394</v>
       </c>
@@ -7619,7 +7619,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="87" s="1" customFormat="1" ht="132" hidden="1" spans="1:13">
+    <row r="87" s="1" customFormat="1" ht="132" spans="1:13">
       <c r="A87" s="8" t="s">
         <v>394</v>
       </c>
@@ -7660,7 +7660,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="88" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="88" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A88" s="8" t="s">
         <v>394</v>
       </c>
@@ -7701,7 +7701,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="89" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
+    <row r="89" s="1" customFormat="1" ht="82.5" spans="1:13">
       <c r="A89" s="8" t="s">
         <v>394</v>
       </c>
@@ -7742,7 +7742,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="90" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
+    <row r="90" s="1" customFormat="1" ht="33" spans="1:13">
       <c r="A90" s="8" t="s">
         <v>394</v>
       </c>
@@ -7783,7 +7783,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="91" s="1" customFormat="1" hidden="1" spans="1:13">
+    <row r="91" s="1" customFormat="1" spans="1:13">
       <c r="A91" s="8" t="s">
         <v>394</v>
       </c>
@@ -7824,7 +7824,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="92" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="92" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A92" s="8" t="s">
         <v>394</v>
       </c>
@@ -7865,7 +7865,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="93" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="93" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A93" s="8" t="s">
         <v>394</v>
       </c>
@@ -7906,7 +7906,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="94" s="1" customFormat="1" ht="115.5" hidden="1" spans="1:13">
+    <row r="94" s="1" customFormat="1" ht="115.5" spans="1:13">
       <c r="A94" s="8" t="s">
         <v>394</v>
       </c>
@@ -7947,7 +7947,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="95" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
+    <row r="95" s="1" customFormat="1" ht="33" spans="1:13">
       <c r="A95" s="8" t="s">
         <v>394</v>
       </c>
@@ -7988,7 +7988,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="96" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
+    <row r="96" s="1" customFormat="1" ht="49.5" spans="1:13">
       <c r="A96" s="8" t="s">
         <v>394</v>
       </c>
@@ -8029,7 +8029,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="97" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
+    <row r="97" s="1" customFormat="1" ht="33" spans="1:13">
       <c r="A97" s="8" t="s">
         <v>394</v>
       </c>
@@ -8070,7 +8070,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="98" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
+    <row r="98" s="1" customFormat="1" ht="49.5" spans="1:13">
       <c r="A98" s="8" t="s">
         <v>394</v>
       </c>
@@ -8111,7 +8111,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="99" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="99" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A99" s="8" t="s">
         <v>394</v>
       </c>
@@ -8152,7 +8152,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="100" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
+    <row r="100" s="1" customFormat="1" ht="49.5" spans="1:13">
       <c r="A100" s="8" t="s">
         <v>394</v>
       </c>
@@ -8193,7 +8193,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="101" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
+    <row r="101" s="1" customFormat="1" ht="82.5" spans="1:13">
       <c r="A101" s="8" t="s">
         <v>394</v>
       </c>
@@ -8234,7 +8234,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="102" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
+    <row r="102" s="1" customFormat="1" ht="33" spans="1:13">
       <c r="A102" s="8" t="s">
         <v>394</v>
       </c>
@@ -8275,7 +8275,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="103" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="103" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A103" s="8" t="s">
         <v>394</v>
       </c>
@@ -8316,7 +8316,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="104" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
+    <row r="104" s="1" customFormat="1" ht="49.5" spans="1:13">
       <c r="A104" s="8" t="s">
         <v>394</v>
       </c>
@@ -8357,7 +8357,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="105" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
+    <row r="105" s="1" customFormat="1" ht="49.5" spans="1:13">
       <c r="A105" s="8" t="s">
         <v>394</v>
       </c>
@@ -8377,28 +8377,28 @@
         <v>308</v>
       </c>
       <c r="G105" s="8" t="s">
-        <v>304</v>
+        <v>502</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="I105" s="9" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="J105" s="8" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="K105" s="8" t="s">
         <v>16</v>
       </c>
       <c r="L105" s="8" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="M105" s="4" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="106" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="106" s="1" customFormat="1" ht="82.5" spans="1:13">
       <c r="A106" s="8" t="s">
         <v>394</v>
       </c>
@@ -8418,7 +8418,7 @@
         <v>303</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>505</v>
+        <v>304</v>
       </c>
       <c r="H106" s="9" t="s">
         <v>506</v>
@@ -8427,19 +8427,19 @@
         <v>507</v>
       </c>
       <c r="J106" s="8" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="K106" s="8" t="s">
         <v>16</v>
       </c>
       <c r="L106" s="8" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="M106" s="4" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="107" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
+    <row r="107" s="1" customFormat="1" ht="82.5" spans="1:13">
       <c r="A107" s="8" t="s">
         <v>394</v>
       </c>
@@ -8480,7 +8480,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="108" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
+    <row r="108" s="1" customFormat="1" ht="33" spans="1:13">
       <c r="A108" s="8" t="s">
         <v>394</v>
       </c>
@@ -8521,7 +8521,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="109" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
+    <row r="109" s="1" customFormat="1" ht="49.5" spans="1:13">
       <c r="A109" s="8" t="s">
         <v>394</v>
       </c>
@@ -8562,7 +8562,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="110" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
+    <row r="110" s="1" customFormat="1" ht="49.5" spans="1:13">
       <c r="A110" s="8" t="s">
         <v>394</v>
       </c>
@@ -8603,7 +8603,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="111" s="1" customFormat="1" ht="132" hidden="1" spans="1:13">
+    <row r="111" s="1" customFormat="1" ht="132" spans="1:13">
       <c r="A111" s="8" t="s">
         <v>394</v>
       </c>
@@ -8644,7 +8644,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="112" s="1" customFormat="1" ht="99" hidden="1" spans="1:13">
+    <row r="112" s="1" customFormat="1" ht="99" spans="1:13">
       <c r="A112" s="8" t="s">
         <v>394</v>
       </c>
@@ -8685,7 +8685,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="113" s="1" customFormat="1" ht="99" hidden="1" spans="1:13">
+    <row r="113" s="1" customFormat="1" ht="99" spans="1:13">
       <c r="A113" s="8" t="s">
         <v>394</v>
       </c>
@@ -8726,7 +8726,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="114" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
+    <row r="114" s="1" customFormat="1" ht="82.5" spans="1:13">
       <c r="A114" s="8" t="s">
         <v>394</v>
       </c>
@@ -8767,7 +8767,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="115" s="1" customFormat="1" ht="132" hidden="1" spans="1:13">
+    <row r="115" s="1" customFormat="1" ht="132" spans="1:13">
       <c r="A115" s="8" t="s">
         <v>394</v>
       </c>
@@ -8808,7 +8808,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="116" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="116" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A116" s="8" t="s">
         <v>394</v>
       </c>
@@ -8849,7 +8849,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="117" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
+    <row r="117" s="1" customFormat="1" ht="49.5" spans="1:13">
       <c r="A117" s="8" t="s">
         <v>394</v>
       </c>
@@ -8890,7 +8890,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="118" s="1" customFormat="1" ht="198" hidden="1" spans="1:13">
+    <row r="118" s="1" customFormat="1" ht="198" spans="1:13">
       <c r="A118" s="8" t="s">
         <v>394</v>
       </c>
@@ -8931,7 +8931,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="119" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="119" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A119" s="8" t="s">
         <v>394</v>
       </c>
@@ -8972,7 +8972,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="120" s="1" customFormat="1" ht="115.5" hidden="1" spans="1:13">
+    <row r="120" s="1" customFormat="1" ht="115.5" spans="1:13">
       <c r="A120" s="8" t="s">
         <v>394</v>
       </c>
@@ -9013,7 +9013,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="121" s="1" customFormat="1" ht="99" hidden="1" spans="1:13">
+    <row r="121" s="1" customFormat="1" ht="99" spans="1:13">
       <c r="A121" s="8" t="s">
         <v>394</v>
       </c>
@@ -9054,7 +9054,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="122" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
+    <row r="122" s="1" customFormat="1" ht="33" spans="1:13">
       <c r="A122" s="2" t="s">
         <v>575</v>
       </c>
@@ -9095,7 +9095,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="123" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
+    <row r="123" s="1" customFormat="1" ht="82.5" spans="1:13">
       <c r="A123" s="2" t="s">
         <v>575</v>
       </c>
@@ -9136,7 +9136,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="124" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
+    <row r="124" s="1" customFormat="1" ht="33" spans="1:13">
       <c r="A124" s="2" t="s">
         <v>575</v>
       </c>
@@ -9177,7 +9177,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="125" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="125" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A125" s="2" t="s">
         <v>575</v>
       </c>
@@ -9218,7 +9218,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="126" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="126" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A126" s="2" t="s">
         <v>575</v>
       </c>
@@ -9259,7 +9259,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="127" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
+    <row r="127" s="1" customFormat="1" ht="33" spans="1:13">
       <c r="A127" s="2" t="s">
         <v>575</v>
       </c>
@@ -9300,7 +9300,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="128" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
+    <row r="128" s="1" customFormat="1" ht="82.5" spans="1:13">
       <c r="A128" s="2" t="s">
         <v>575</v>
       </c>
@@ -9341,7 +9341,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="129" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="129" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A129" s="2" t="s">
         <v>575</v>
       </c>
@@ -9382,7 +9382,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="130" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="130" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A130" s="2" t="s">
         <v>575</v>
       </c>
@@ -9423,7 +9423,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="131" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
+    <row r="131" s="1" customFormat="1" ht="82.5" spans="1:13">
       <c r="A131" s="2" t="s">
         <v>575</v>
       </c>
@@ -9464,7 +9464,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="132" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
+    <row r="132" s="1" customFormat="1" ht="33" spans="1:13">
       <c r="A132" s="2" t="s">
         <v>575</v>
       </c>
@@ -9505,7 +9505,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="133" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
+    <row r="133" s="1" customFormat="1" ht="33" spans="1:13">
       <c r="A133" s="2" t="s">
         <v>575</v>
       </c>
@@ -9546,7 +9546,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="134" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
+    <row r="134" s="1" customFormat="1" ht="33" spans="1:13">
       <c r="A134" s="2" t="s">
         <v>575</v>
       </c>
@@ -9587,7 +9587,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="135" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="135" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A135" s="2" t="s">
         <v>575</v>
       </c>
@@ -9628,7 +9628,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="136" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
+    <row r="136" s="1" customFormat="1" ht="82.5" spans="1:13">
       <c r="A136" s="2" t="s">
         <v>575</v>
       </c>
@@ -9669,7 +9669,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="137" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
+    <row r="137" s="1" customFormat="1" ht="33" spans="1:13">
       <c r="A137" s="2" t="s">
         <v>575</v>
       </c>
@@ -9710,7 +9710,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="138" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
+    <row r="138" s="1" customFormat="1" ht="82.5" spans="1:13">
       <c r="A138" s="2" t="s">
         <v>575</v>
       </c>
@@ -9751,7 +9751,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="139" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="139" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A139" s="2" t="s">
         <v>575</v>
       </c>
@@ -9792,7 +9792,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="140" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
+    <row r="140" s="1" customFormat="1" ht="33" spans="1:13">
       <c r="A140" s="2" t="s">
         <v>575</v>
       </c>
@@ -9833,7 +9833,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="141" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="141" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A141" s="2" t="s">
         <v>575</v>
       </c>
@@ -9874,7 +9874,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="142" s="1" customFormat="1" ht="115.5" hidden="1" spans="1:13">
+    <row r="142" s="1" customFormat="1" ht="115.5" spans="1:13">
       <c r="A142" s="2" t="s">
         <v>575</v>
       </c>
@@ -9906,7 +9906,7 @@
         <v>35</v>
       </c>
       <c r="K142" s="8" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="L142" s="8" t="s">
         <v>36</v>
@@ -9915,7 +9915,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="143" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="143" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A143" s="2" t="s">
         <v>575</v>
       </c>
@@ -9956,7 +9956,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="144" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="144" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A144" s="2" t="s">
         <v>575</v>
       </c>
@@ -9997,7 +9997,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="145" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
+    <row r="145" s="1" customFormat="1" ht="49.5" spans="1:13">
       <c r="A145" s="2" t="s">
         <v>575</v>
       </c>
@@ -10038,7 +10038,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="146" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
+    <row r="146" s="1" customFormat="1" ht="49.5" spans="1:13">
       <c r="A146" s="2" t="s">
         <v>575</v>
       </c>
@@ -10079,7 +10079,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="147" s="1" customFormat="1" ht="181.5" hidden="1" spans="1:13">
+    <row r="147" s="1" customFormat="1" ht="181.5" spans="1:13">
       <c r="A147" s="2" t="s">
         <v>575</v>
       </c>
@@ -10120,7 +10120,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="148" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
+    <row r="148" s="1" customFormat="1" ht="49.5" spans="1:13">
       <c r="A148" s="2" t="s">
         <v>575</v>
       </c>
@@ -10161,7 +10161,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="149" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
+    <row r="149" s="1" customFormat="1" ht="49.5" spans="1:13">
       <c r="A149" s="2" t="s">
         <v>575</v>
       </c>
@@ -10202,7 +10202,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="150" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
+    <row r="150" s="1" customFormat="1" ht="49.5" spans="1:13">
       <c r="A150" s="2" t="s">
         <v>575</v>
       </c>
@@ -10243,7 +10243,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="151" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
+    <row r="151" s="1" customFormat="1" ht="49.5" spans="1:13">
       <c r="A151" s="2" t="s">
         <v>575</v>
       </c>
@@ -10263,7 +10263,7 @@
         <v>700</v>
       </c>
       <c r="G151" s="8" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="H151" s="9" t="s">
         <v>701</v>
@@ -10284,7 +10284,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="152" s="1" customFormat="1" ht="165" hidden="1" spans="1:13">
+    <row r="152" s="1" customFormat="1" ht="165" spans="1:13">
       <c r="A152" s="2" t="s">
         <v>575</v>
       </c>
@@ -10325,7 +10325,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="153" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="153" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A153" s="2" t="s">
         <v>575</v>
       </c>
@@ -10366,7 +10366,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="154" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
+    <row r="154" s="1" customFormat="1" ht="82.5" spans="1:13">
       <c r="A154" s="2" t="s">
         <v>575</v>
       </c>
@@ -10407,7 +10407,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="155" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
+    <row r="155" s="1" customFormat="1" ht="49.5" spans="1:13">
       <c r="A155" s="2" t="s">
         <v>575</v>
       </c>
@@ -10448,7 +10448,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="156" s="1" customFormat="1" ht="49.5" hidden="1" spans="1:13">
+    <row r="156" s="1" customFormat="1" ht="49.5" spans="1:13">
       <c r="A156" s="2" t="s">
         <v>575</v>
       </c>
@@ -10489,7 +10489,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="157" s="1" customFormat="1" ht="33" hidden="1" spans="1:13">
+    <row r="157" s="1" customFormat="1" ht="33" spans="1:13">
       <c r="A157" s="2" t="s">
         <v>575</v>
       </c>
@@ -10530,7 +10530,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="158" s="1" customFormat="1" ht="66" hidden="1" spans="1:13">
+    <row r="158" s="1" customFormat="1" ht="66" spans="1:13">
       <c r="A158" s="2" t="s">
         <v>575</v>
       </c>
@@ -10571,7 +10571,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="159" s="1" customFormat="1" ht="132" hidden="1" spans="1:13">
+    <row r="159" s="1" customFormat="1" ht="132" spans="1:13">
       <c r="A159" s="2" t="s">
         <v>575</v>
       </c>
@@ -10612,7 +10612,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="160" s="1" customFormat="1" ht="82.5" hidden="1" spans="1:13">
+    <row r="160" s="1" customFormat="1" ht="82.5" spans="1:13">
       <c r="A160" s="2" t="s">
         <v>575</v>
       </c>
@@ -10635,7 +10635,7 @@
         <v>304</v>
       </c>
       <c r="H160" s="9" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="I160" s="9" t="s">
         <v>743</v>
@@ -10653,7 +10653,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="161" ht="66" hidden="1" spans="1:13">
+    <row r="161" ht="66" spans="1:13">
       <c r="A161" s="2" t="s">
         <v>575</v>
       </c>
@@ -10694,7 +10694,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="162" ht="330" hidden="1" spans="1:13">
+    <row r="162" ht="330" spans="1:13">
       <c r="A162" s="2" t="s">
         <v>750</v>
       </c>
@@ -10735,7 +10735,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="163" hidden="1" spans="1:13">
+    <row r="163" spans="1:13">
       <c r="A163" s="2" t="s">
         <v>750</v>
       </c>
@@ -10776,7 +10776,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="164" hidden="1" spans="1:13">
+    <row r="164" spans="1:13">
       <c r="A164" s="2" t="s">
         <v>750</v>
       </c>
@@ -10817,7 +10817,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="165" hidden="1" spans="1:13">
+    <row r="165" spans="1:13">
       <c r="A165" s="2" t="s">
         <v>750</v>
       </c>
@@ -10858,7 +10858,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="166" hidden="1" spans="1:13">
+    <row r="166" spans="1:13">
       <c r="A166" s="2" t="s">
         <v>750</v>
       </c>
@@ -10899,7 +10899,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="167" hidden="1" spans="1:13">
+    <row r="167" spans="1:13">
       <c r="A167" s="2" t="s">
         <v>750</v>
       </c>
@@ -10940,7 +10940,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="168" hidden="1" spans="1:13">
+    <row r="168" spans="1:13">
       <c r="A168" s="2" t="s">
         <v>750</v>
       </c>
@@ -10981,7 +10981,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="169" ht="33" hidden="1" spans="1:13">
+    <row r="169" ht="33" spans="1:13">
       <c r="A169" s="2" t="s">
         <v>750</v>
       </c>
@@ -11022,7 +11022,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="170" hidden="1" spans="1:13">
+    <row r="170" spans="1:13">
       <c r="A170" s="2" t="s">
         <v>750</v>
       </c>
@@ -11063,7 +11063,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="171" hidden="1" spans="1:13">
+    <row r="171" spans="1:13">
       <c r="A171" s="2" t="s">
         <v>750</v>
       </c>
@@ -11104,7 +11104,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="172" hidden="1" spans="1:13">
+    <row r="172" spans="1:13">
       <c r="A172" s="2" t="s">
         <v>750</v>
       </c>
@@ -11145,7 +11145,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="173" hidden="1" spans="1:13">
+    <row r="173" spans="1:13">
       <c r="A173" s="2" t="s">
         <v>750</v>
       </c>
@@ -11186,7 +11186,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="174" hidden="1" spans="1:13">
+    <row r="174" spans="1:13">
       <c r="A174" s="2" t="s">
         <v>750</v>
       </c>
@@ -11227,7 +11227,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="175" hidden="1" spans="1:13">
+    <row r="175" spans="1:13">
       <c r="A175" s="2" t="s">
         <v>750</v>
       </c>
@@ -11268,7 +11268,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="176" hidden="1" spans="1:13">
+    <row r="176" spans="1:13">
       <c r="A176" s="2" t="s">
         <v>750</v>
       </c>
@@ -11309,7 +11309,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="177" hidden="1" spans="1:13">
+    <row r="177" spans="1:13">
       <c r="A177" s="2" t="s">
         <v>750</v>
       </c>
@@ -11350,7 +11350,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="178" hidden="1" spans="1:13">
+    <row r="178" spans="1:13">
       <c r="A178" s="2" t="s">
         <v>750</v>
       </c>
@@ -11391,7 +11391,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="179" hidden="1" spans="1:13">
+    <row r="179" spans="1:13">
       <c r="A179" s="2" t="s">
         <v>750</v>
       </c>
@@ -11432,7 +11432,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="180" hidden="1" spans="1:13">
+    <row r="180" spans="1:13">
       <c r="A180" s="2" t="s">
         <v>750</v>
       </c>
@@ -11473,7 +11473,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="181" hidden="1" spans="1:13">
+    <row r="181" spans="1:13">
       <c r="A181" s="2" t="s">
         <v>750</v>
       </c>
@@ -11514,7 +11514,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="182" ht="33" hidden="1" spans="1:13">
+    <row r="182" ht="33" spans="1:13">
       <c r="A182" s="2" t="s">
         <v>750</v>
       </c>
@@ -11555,7 +11555,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="183" ht="49.5" hidden="1" spans="1:13">
+    <row r="183" ht="49.5" spans="1:13">
       <c r="A183" s="2" t="s">
         <v>750</v>
       </c>
@@ -11596,7 +11596,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="184" ht="49.5" hidden="1" spans="1:13">
+    <row r="184" ht="49.5" spans="1:13">
       <c r="A184" s="2" t="s">
         <v>750</v>
       </c>
@@ -11637,7 +11637,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="185" ht="49.5" hidden="1" spans="1:13">
+    <row r="185" ht="49.5" spans="1:13">
       <c r="A185" s="2" t="s">
         <v>750</v>
       </c>
@@ -11678,7 +11678,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="186" ht="49.5" hidden="1" spans="1:13">
+    <row r="186" ht="49.5" spans="1:13">
       <c r="A186" s="2" t="s">
         <v>750</v>
       </c>
@@ -11719,7 +11719,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="187" ht="66" hidden="1" spans="1:13">
+    <row r="187" ht="66" spans="1:13">
       <c r="A187" s="2" t="s">
         <v>750</v>
       </c>
@@ -11760,7 +11760,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="188" ht="82.5" hidden="1" spans="1:13">
+    <row r="188" ht="82.5" spans="1:13">
       <c r="A188" s="2" t="s">
         <v>750</v>
       </c>
@@ -11801,7 +11801,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="189" ht="66" hidden="1" spans="1:13">
+    <row r="189" ht="66" spans="1:13">
       <c r="A189" s="2" t="s">
         <v>750</v>
       </c>
@@ -11842,7 +11842,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="190" ht="33" hidden="1" spans="1:13">
+    <row r="190" ht="33" spans="1:13">
       <c r="A190" s="2" t="s">
         <v>750</v>
       </c>
@@ -11883,7 +11883,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="191" ht="33" hidden="1" spans="1:13">
+    <row r="191" ht="33" spans="1:13">
       <c r="A191" s="2" t="s">
         <v>750</v>
       </c>
@@ -11924,7 +11924,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="192" ht="33" hidden="1" spans="1:13">
+    <row r="192" ht="33" spans="1:13">
       <c r="A192" s="2" t="s">
         <v>750</v>
       </c>
@@ -11965,7 +11965,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="193" ht="49.5" hidden="1" spans="1:13">
+    <row r="193" ht="49.5" spans="1:13">
       <c r="A193" s="2" t="s">
         <v>750</v>
       </c>
@@ -12006,7 +12006,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="194" ht="82.5" hidden="1" spans="1:13">
+    <row r="194" ht="82.5" spans="1:13">
       <c r="A194" s="2" t="s">
         <v>750</v>
       </c>
@@ -12047,7 +12047,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="195" ht="66" hidden="1" spans="1:13">
+    <row r="195" ht="66" spans="1:13">
       <c r="A195" s="2" t="s">
         <v>750</v>
       </c>
@@ -12088,7 +12088,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="196" ht="33" hidden="1" spans="1:13">
+    <row r="196" ht="33" spans="1:13">
       <c r="A196" s="2" t="s">
         <v>750</v>
       </c>
@@ -12129,7 +12129,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="197" ht="33" hidden="1" spans="1:13">
+    <row r="197" ht="33" spans="1:13">
       <c r="A197" s="2" t="s">
         <v>750</v>
       </c>
@@ -12170,7 +12170,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="198" ht="33" hidden="1" spans="1:13">
+    <row r="198" ht="33" spans="1:13">
       <c r="A198" s="2" t="s">
         <v>750</v>
       </c>
@@ -12211,7 +12211,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="199" ht="33" hidden="1" spans="1:13">
+    <row r="199" ht="33" spans="1:13">
       <c r="A199" s="2" t="s">
         <v>750</v>
       </c>
@@ -12252,7 +12252,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="200" ht="33" hidden="1" spans="1:13">
+    <row r="200" ht="33" spans="1:13">
       <c r="A200" s="2" t="s">
         <v>750</v>
       </c>
@@ -12293,7 +12293,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="201" ht="49.5" hidden="1" spans="1:13">
+    <row r="201" ht="49.5" spans="1:13">
       <c r="A201" s="2" t="s">
         <v>750</v>
       </c>
@@ -12336,11 +12336,6 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:M201" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="TNT Vape"/>
-      </filters>
-    </filterColumn>
     <extLst/>
   </autoFilter>
   <hyperlinks>
